--- a/exports/updated_data.xlsx
+++ b/exports/updated_data.xlsx
@@ -11,174 +11,144 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="56">
-  <si>
-    <t>reportName</t>
-  </si>
-  <si>
-    <t>generationDate</t>
-  </si>
-  <si>
-    <t>agentDetails_name</t>
-  </si>
-  <si>
-    <t>agentDetails_email</t>
-  </si>
-  <si>
-    <t>reportSummary_periodType</t>
-  </si>
-  <si>
-    <t>reportSummary_netQuantity</t>
-  </si>
-  <si>
-    <t>stockTransactions_1_date</t>
-  </si>
-  <si>
-    <t>stockTransactions_1_product</t>
-  </si>
-  <si>
-    <t>stockTransactions_1_txnId</t>
-  </si>
-  <si>
-    <t>stockTransactions_1_status</t>
-  </si>
-  <si>
-    <t>stockTransactions_1_quantity</t>
-  </si>
-  <si>
-    <t>stockTransactions_2_date</t>
-  </si>
-  <si>
-    <t>stockTransactions_2_product</t>
-  </si>
-  <si>
-    <t>stockTransactions_2_txnId</t>
-  </si>
-  <si>
-    <t>stockTransactions_2_status</t>
-  </si>
-  <si>
-    <t>stockTransactions_2_quantity</t>
-  </si>
-  <si>
-    <t>stockTransactions_3_date</t>
-  </si>
-  <si>
-    <t>stockTransactions_3_product</t>
-  </si>
-  <si>
-    <t>stockTransactions_3_txnId</t>
-  </si>
-  <si>
-    <t>stockTransactions_3_status</t>
-  </si>
-  <si>
-    <t>stockTransactions_3_quantity</t>
-  </si>
-  <si>
-    <t>stockTransactions_4_date</t>
-  </si>
-  <si>
-    <t>stockTransactions_4_product</t>
-  </si>
-  <si>
-    <t>stockTransactions_4_txnId</t>
-  </si>
-  <si>
-    <t>stockTransactions_4_status</t>
-  </si>
-  <si>
-    <t>stockTransactions_4_quantity</t>
-  </si>
-  <si>
-    <t>stockTransactions_5_date</t>
-  </si>
-  <si>
-    <t>stockTransactions_5_product</t>
-  </si>
-  <si>
-    <t>stockTransactions_5_txnId</t>
-  </si>
-  <si>
-    <t>stockTransactions_5_status</t>
-  </si>
-  <si>
-    <t>stockTransactions_5_quantity</t>
-  </si>
-  <si>
-    <t>stockTransactions_6_date</t>
-  </si>
-  <si>
-    <t>stockTransactions_6_product</t>
-  </si>
-  <si>
-    <t>stockTransactions_6_txnId</t>
-  </si>
-  <si>
-    <t>stockTransactions_6_status</t>
-  </si>
-  <si>
-    <t>stockTransactions_6_quantity</t>
-  </si>
-  <si>
-    <t>stockSummary_stockIn</t>
-  </si>
-  <si>
-    <t>stockSummary_stockOut</t>
-  </si>
-  <si>
-    <t>stockSummary_netChange</t>
-  </si>
-  <si>
-    <t>Stock Report</t>
-  </si>
-  <si>
-    <t>2/10/2026 12:13:25 PM</t>
-  </si>
-  <si>
-    <t>Jatin Jain</t>
-  </si>
-  <si>
-    <t>jjain0740@gmail.com</t>
-  </si>
-  <si>
-    <t>All</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="46">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>TXN ID</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>1_Date</t>
+  </si>
+  <si>
+    <t>1_Product</t>
+  </si>
+  <si>
+    <t>1_TXN ID</t>
+  </si>
+  <si>
+    <t>1_Status</t>
+  </si>
+  <si>
+    <t>1_Quantity</t>
+  </si>
+  <si>
+    <t>2_Date</t>
+  </si>
+  <si>
+    <t>2_Product</t>
+  </si>
+  <si>
+    <t>2_TXN ID</t>
+  </si>
+  <si>
+    <t>2_Status</t>
+  </si>
+  <si>
+    <t>2_Quantity</t>
+  </si>
+  <si>
+    <t>3_Date</t>
+  </si>
+  <si>
+    <t>3_Product</t>
+  </si>
+  <si>
+    <t>3_TXN ID</t>
+  </si>
+  <si>
+    <t>3_Status</t>
+  </si>
+  <si>
+    <t>3_Quantity</t>
+  </si>
+  <si>
+    <t>4_Date</t>
+  </si>
+  <si>
+    <t>4_Product</t>
+  </si>
+  <si>
+    <t>4_TXN ID</t>
+  </si>
+  <si>
+    <t>4_Status</t>
+  </si>
+  <si>
+    <t>4_Quantity</t>
+  </si>
+  <si>
+    <t>5_Date</t>
+  </si>
+  <si>
+    <t>5_Product</t>
+  </si>
+  <si>
+    <t>5_TXN ID</t>
+  </si>
+  <si>
+    <t>5_Status</t>
+  </si>
+  <si>
+    <t>5_Quantity</t>
+  </si>
+  <si>
+    <t>Feb 4, 2026</t>
+  </si>
+  <si>
+    <t>I may disagree with what you say, but I will defend to death your right to say it. (Evelyn Beatrice Hall)</t>
+  </si>
+  <si>
+    <t>OUTSTK_11109</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>-1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Laptop 1</t>
+  </si>
+  <si>
+    <t>nackband</t>
+  </si>
+  <si>
+    <t>-2</t>
   </si>
   <si>
     <t>Feb 9, 2026</t>
   </si>
   <si>
-    <t>Mini DryTab Lime Automatic Toilet Bowl Cleaner-Freshener</t>
+    <t>Mini DryTab Lime  Automatic Toilet Bowl Cleaner-Freshener</t>
+  </si>
+  <si>
+    <t>INSTK_35310</t>
+  </si>
+  <si>
+    <t>REJECTED</t>
+  </si>
+  <si>
+    <t>+1</t>
   </si>
   <si>
     <t>OUTSTK_64111</t>
   </si>
   <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>INSTK_35310</t>
-  </si>
-  <si>
-    <t>REJECTED</t>
-  </si>
-  <si>
     <t>test</t>
-  </si>
-  <si>
-    <t>Feb 4, 2026</t>
-  </si>
-  <si>
-    <t>I may disagree with what you say, but I will defend to death your right to say it. (Evelyn Beatrice Hall)</t>
-  </si>
-  <si>
-    <t>OUTSTK_11109</t>
-  </si>
-  <si>
-    <t>Laptop 1</t>
-  </si>
-  <si>
-    <t>nackband</t>
   </si>
 </sst>
 </file>
@@ -559,10 +529,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -653,151 +623,557 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="B2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="C2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="D2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="E2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" s="1" t="s">
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>35</v>
+      </c>
+      <c r="R3" t="s">
+        <v>35</v>
+      </c>
+      <c r="S3" t="s">
+        <v>35</v>
+      </c>
+      <c r="T3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U3" t="s">
+        <v>35</v>
+      </c>
+      <c r="V3" t="s">
+        <v>35</v>
+      </c>
+      <c r="W3" t="s">
+        <v>35</v>
+      </c>
+      <c r="X3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4" t="s">
         <v>38</v>
       </c>
+      <c r="P4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>35</v>
+      </c>
+      <c r="R4" t="s">
+        <v>35</v>
+      </c>
+      <c r="S4" t="s">
+        <v>35</v>
+      </c>
+      <c r="T4" t="s">
+        <v>35</v>
+      </c>
+      <c r="U4" t="s">
+        <v>35</v>
+      </c>
+      <c r="V4" t="s">
+        <v>35</v>
+      </c>
+      <c r="W4" t="s">
+        <v>35</v>
+      </c>
+      <c r="X4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" t="s">
+        <v>35</v>
+      </c>
+      <c r="O5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P5" t="s">
         <v>39</v>
       </c>
-      <c r="B2" t="s">
+      <c r="Q5" t="s">
         <v>40</v>
       </c>
-      <c r="C2" t="s">
+      <c r="R5" t="s">
         <v>41</v>
       </c>
-      <c r="D2" t="s">
+      <c r="S5" t="s">
         <v>42</v>
       </c>
-      <c r="E2" t="s">
+      <c r="T5" t="s">
         <v>43</v>
       </c>
-      <c r="F2">
-        <v>-3</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="U5" t="s">
+        <v>35</v>
+      </c>
+      <c r="V5" t="s">
+        <v>35</v>
+      </c>
+      <c r="W5" t="s">
+        <v>35</v>
+      </c>
+      <c r="X5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P6" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R6" t="s">
+        <v>35</v>
+      </c>
+      <c r="S6" t="s">
+        <v>35</v>
+      </c>
+      <c r="T6" t="s">
+        <v>35</v>
+      </c>
+      <c r="U6" t="s">
+        <v>39</v>
+      </c>
+      <c r="V6" t="s">
+        <v>40</v>
+      </c>
+      <c r="W6" t="s">
         <v>44</v>
       </c>
-      <c r="H2" t="s">
+      <c r="X6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7" t="s">
+        <v>35</v>
+      </c>
+      <c r="O7" t="s">
+        <v>35</v>
+      </c>
+      <c r="P7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>35</v>
+      </c>
+      <c r="R7" t="s">
+        <v>35</v>
+      </c>
+      <c r="S7" t="s">
+        <v>35</v>
+      </c>
+      <c r="T7" t="s">
+        <v>35</v>
+      </c>
+      <c r="U7" t="s">
+        <v>35</v>
+      </c>
+      <c r="V7" t="s">
+        <v>35</v>
+      </c>
+      <c r="W7" t="s">
+        <v>35</v>
+      </c>
+      <c r="X7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA7" t="s">
         <v>45</v>
       </c>
-      <c r="I2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K2">
-        <v>-1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N2" t="s">
-        <v>48</v>
-      </c>
-      <c r="O2" t="s">
-        <v>49</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>44</v>
-      </c>
-      <c r="R2" t="s">
-        <v>50</v>
-      </c>
-      <c r="S2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T2" t="s">
-        <v>49</v>
-      </c>
-      <c r="U2">
-        <v>1</v>
-      </c>
-      <c r="V2" t="s">
-        <v>51</v>
-      </c>
-      <c r="W2" t="s">
-        <v>52</v>
-      </c>
-      <c r="X2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z2">
-        <v>-1</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE2">
-        <v>-1</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AJ2">
-        <v>-2</v>
-      </c>
-      <c r="AK2">
-        <v>2</v>
-      </c>
-      <c r="AL2">
-        <v>-5</v>
-      </c>
-      <c r="AM2">
-        <v>-3</v>
+      <c r="AB7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
